--- a/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-practitioner.xlsx
+++ b/nr-prepare-release-1.1.0-final/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T16:54:59+00:00</t>
+    <t>2025-02-11T12:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>102</v>
@@ -23959,7 +23959,7 @@
         <v>86</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>84</v>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>102</v>
@@ -25175,7 +25175,7 @@
         <v>85</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>84</v>
